--- a/Costo_Personalizado.xlsx
+++ b/Costo_Personalizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maurobenetti/Documents/PhD/Python/ISEC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA41BBA8-F73C-1041-A98B-020E9AFB5DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7822E44C-A5A8-EB46-9E4E-1AB7CE3BA333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16980" xr2:uid="{C091BC44-D062-3D4C-A041-870970761D09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Character1</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>l</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5EAC829-88C7-6445-A588-F93444FA00D6}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -515,6 +521,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
